--- a/POPULATION_10092026/Africa_Population_Collector_Progress_Report.xlsx
+++ b/POPULATION_10092026/Africa_Population_Collector_Progress_Report.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NSO (INE)</t>
+          <t>NSO (Instituto Nacional de Estatística)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSO (INE)</t>
+          <t>NSO (Instituto Nacional de Estatística)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSO (INS)</t>
+          <t>NSO (Institut National de la Statistique)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NSO (INS)</t>
+          <t>NSO (Institut National de la Statistique)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>static_url (Tier-1 API)</t>
+          <t>NSO data API (Tier-1 API)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NSO (INE)</t>
+          <t>NSO (Instituto Nacional de Estatistica)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSO (NSO)</t>
+          <t>NSO (National Statistical Office)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NSO (INS)</t>
+          <t>NSO (Institut National de la Statistique)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NSO (NBS)</t>
+          <t>NSO (National Bureau of Statistics)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NSO (NBS)</t>
+          <t>NSO (National Bureau of Statistics)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NSO (NBS)</t>
+          <t>NSO (National Bureau of Statistics)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NSO (INS)</t>
+          <t>NSO (Institut National de la Statistique)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
